--- a/data/trans_camb/IP13-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP13-Habitat-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,83</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-0,73</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,74</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,79</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-2,47</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-1,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,83</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-0,73</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,33</t>
+          <t>-0,96</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,31</t>
+          <t>-0,07</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 5,85</t>
+          <t>-3,1; 4,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 1,42</t>
+          <t>-4,46; 3,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 3,36</t>
+          <t>-3,31; 5,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 4,74</t>
+          <t>-3,78; 5,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 2,98</t>
+          <t>-6,42; 1,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 4,23</t>
+          <t>-4,85; 3,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 3,89</t>
+          <t>-2,03; 4,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 1,52</t>
+          <t>-4,7; 1,1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 2,81</t>
+          <t>-2,99; 3,02</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>21,03%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-18,39%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>18,71%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>14,4%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-44,9%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-18,3%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>21,03%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-18,39%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>-17,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-6,56%</t>
+          <t>-1,49%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-51,75; 182,17</t>
+          <t>-57,17; 184,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-84,78; 78,58</t>
+          <t>-78,01; 166,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-72,86; 116,79</t>
+          <t>-60,52; 257,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-54,54; 233,86</t>
+          <t>-53,56; 160,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-78,4; 152,0</t>
+          <t>-84,27; 45,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-63,95; 188,4</t>
+          <t>-68,44; 128,67</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-39,52; 115,39</t>
+          <t>-35,78; 150,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-70,19; 46,58</t>
+          <t>-70,66; 38,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-52,84; 85,17</t>
+          <t>-49,63; 88,15</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,66</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,79</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-0,39</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1,25</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,77</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,42</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,66</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-0,79</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,66</t>
+          <t>0,11</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,16</t>
+          <t>-0,14</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 4,49</t>
+          <t>-4,22; 2,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 4,36</t>
+          <t>-4,38; 2,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 3,76</t>
+          <t>-4,01; 3,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 3,23</t>
+          <t>-2,11; 5,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 2,66</t>
+          <t>-2,62; 4,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 2,81</t>
+          <t>-3,27; 3,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 2,65</t>
+          <t>-2,34; 2,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 2,48</t>
+          <t>-2,6; 2,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 2,33</t>
+          <t>-2,72; 2,43</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-11,07%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-13,2%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-6,6%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>24,59%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>15,14%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>8,23%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-11,07%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-13,2%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-11,13%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-2,81%</t>
+          <t>-2,49%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-36,97; 128,23</t>
+          <t>-53,47; 68,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-38,39; 123,78</t>
+          <t>-56,0; 71,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-47,21; 102,93</t>
+          <t>-49,9; 80,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-57,42; 86,03</t>
+          <t>-32,49; 153,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-55,97; 74,0</t>
+          <t>-41,04; 140,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-53,17; 70,1</t>
+          <t>-50,09; 106,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-34,56; 60,98</t>
+          <t>-34,32; 61,19</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-34,26; 54,75</t>
+          <t>-38,84; 62,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-39,49; 53,91</t>
+          <t>-40,12; 57,61</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>3,94</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,85</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2,27</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-1,79</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-0,32</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,45</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3,94</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,85</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,32</t>
+          <t>1,14</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,95</t>
+          <t>1,73</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 2,64</t>
+          <t>-0,29; 8,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 4,74</t>
+          <t>-3,38; 4,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 3,84</t>
+          <t>-1,83; 7,07</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 8,22</t>
+          <t>-6,51; 2,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 5,0</t>
+          <t>-4,76; 3,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 6,84</t>
+          <t>-3,61; 6,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 4,24</t>
+          <t>-1,79; 4,45</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 3,07</t>
+          <t>-2,57; 3,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 4,57</t>
+          <t>-1,5; 5,35</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>74,44%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>16,02%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>42,87%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-27,22%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-4,92%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-6,85%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>74,44%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>16,02%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>29,21%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-71,31; 62,77</t>
+          <t>-8,18; 241,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-52,83; 124,36</t>
+          <t>-46,97; 139,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-59,51; 92,85</t>
+          <t>-28,61; 221,24</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-11,04; 246,98</t>
+          <t>-71,84; 64,74</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-48,26; 169,0</t>
+          <t>-50,12; 94,83</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-35,68; 193,36</t>
+          <t>-41,32; 145,29</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-27,69; 95,41</t>
+          <t>-25,04; 100,75</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-40,68; 70,73</t>
+          <t>-35,0; 69,37</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-32,26; 104,24</t>
+          <t>-22,52; 121,32</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1,02</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-1,53</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3,58</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>2,66</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>3,54</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>4,17</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,02</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-1,53</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,59</t>
+          <t>3,95</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3,93</t>
+          <t>3,78</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,14; 5,79</t>
+          <t>-2,43; 4,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,72; 6,83</t>
+          <t>-4,73; 1,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,21; 8,14</t>
+          <t>-0,2; 8,17</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 4,54</t>
+          <t>-0,1; 5,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 1,79</t>
+          <t>0,89; 6,82</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 8,25</t>
+          <t>0,94; 7,65</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 4,23</t>
+          <t>-0,26; 4,31</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 3,29</t>
+          <t>-0,96; 3,29</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,37; 7,04</t>
+          <t>1,09; 6,66</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>22,25%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-33,51%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>78,11%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>148,85%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>197,98%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>232,95%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>22,25%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-33,51%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>220,76%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>123,59%</t>
+          <t>118,8%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 711,67</t>
+          <t>-42,9; 177,95</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4,42; 686,16</t>
+          <t>-71,98; 64,19</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>27,59; 990,84</t>
+          <t>-9,49; 253,8</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-48,42; 145,85</t>
+          <t>-17,01; 674,95</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-73,38; 75,6</t>
+          <t>6,91; 907,62</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-14,63; 269,42</t>
+          <t>9,38; 1087,07</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-11,61; 200,21</t>
+          <t>-13,05; 176,29</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-29,74; 142,64</t>
+          <t>-24,84; 165,02</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>30,23; 305,39</t>
+          <t>22,91; 290,06</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1,14</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,58</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1,52</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>0,97</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>0,8</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>1,16</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1,14</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-0,58</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,36</t>
+          <t>1,38</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1,28</t>
+          <t>1,46</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 2,78</t>
+          <t>-0,66; 3,11</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 2,64</t>
+          <t>-2,34; 1,18</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 3,06</t>
+          <t>-0,35; 3,78</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 3,16</t>
+          <t>-0,95; 3,02</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 1,15</t>
+          <t>-1,0; 2,54</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 3,45</t>
+          <t>-0,47; 3,49</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 2,49</t>
+          <t>-0,28; 2,42</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 1,37</t>
+          <t>-1,15; 1,43</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 2,71</t>
+          <t>0,05; 2,94</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>22,88%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-11,68%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>30,34%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>21,79%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>17,84%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>26,01%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>22,88%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-11,68%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>30,8%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-18,6; 78,53</t>
+          <t>-11,32; 73,41</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-18,79; 74,82</t>
+          <t>-38,8; 30,54</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-16,25; 84,96</t>
+          <t>-6,34; 88,09</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-12,7; 75,61</t>
+          <t>-17,93; 85,0</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-41,96; 27,4</t>
+          <t>-18,98; 69,03</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-9,45; 84,85</t>
+          <t>-9,31; 102,35</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 59,6</t>
+          <t>-5,8; 57,89</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-23,0; 33,84</t>
+          <t>-21,97; 34,04</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 65,8</t>
+          <t>0,28; 70,19</t>
         </is>
       </c>
     </row>
